--- a/laporan-keuangan.xlsx
+++ b/laporan-keuangan.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>13294000</v>
@@ -454,7 +454,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>1. 000 - markup solar</v>
       </c>
     </row>
     <row r="3">
@@ -474,16 +474,13 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="G3">
         <v>10426000</v>
       </c>
       <c r="H3">
         <v>0</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -512,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>1. 000 - Tambahkan pembayaran solar</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>1. 300.000 - keperluan di lokasi</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +567,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>1. 340.000 - cashbon  Classmild isi 20 (Wayan)</v>
       </c>
     </row>
     <row r="7">
@@ -598,9 +595,6 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -627,16 +621,13 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>2026-05-09</v>
       </c>
       <c r="B9">
-        <v>3202000</v>
+        <v>702000</v>
       </c>
       <c r="C9">
         <v>1716000</v>
@@ -651,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>486000</v>
+        <v>-2014000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>1. 000.000 - bayar gaji ibu dapur</v>
       </c>
     </row>
     <row r="10">
@@ -665,7 +656,7 @@
         <v>2026-05-10</v>
       </c>
       <c r="B10">
-        <v>5486000</v>
+        <v>-2014000</v>
       </c>
       <c r="C10">
         <v>1700500</v>
@@ -680,13 +671,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>2845500</v>
+        <v>-4654500</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>1.150.000 - cashbon rokok (5 bks Lucky Stike 150 ribu (Pak Noge), 8 Bks Rocker (PakYanto), 1 Slop Classmild 286 ribu, 1 Slop Sampoerna 352 ribu)</v>
       </c>
     </row>
     <row r="11">
@@ -744,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>1. 907.000 Uang dibawa ke Lokasi</v>
       </c>
     </row>
     <row r="13">
@@ -752,7 +743,7 @@
         <v>2026-05-13</v>
       </c>
       <c r="B13">
-        <v>12661500</v>
+        <v>2661500</v>
       </c>
       <c r="C13">
         <v>11284000</v>
@@ -767,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>929500</v>
+        <v>-9070500</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>1. 448.000 - cashbon Bolang (1 Slop Brand Jati dan 1 Bks Surya Besar)</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +772,7 @@
         <v>2026-05-14</v>
       </c>
       <c r="B14">
-        <v>929500</v>
+        <v>911500</v>
       </c>
       <c r="C14">
         <v>315000</v>
@@ -796,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>614500</v>
+        <v>596500</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -810,7 +801,7 @@
         <v>2026-05-15</v>
       </c>
       <c r="B15">
-        <v>11114500</v>
+        <v>596500</v>
       </c>
       <c r="C15">
         <v>10127000</v>
@@ -825,23 +816,15 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>407500</v>
+        <v>-10110500</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 80.000 - markup solar_x000d_
-2. 110.000 - Tambahkan pembayaran solar_x000d_
-3. 300.000 - keperluan di lokasi_x000d_
-4. 340.000 - cashbon  Classmild isi 20 (Wayan)_x000d_
-5. 1.000.000 - bayar gaji ibu dapur_x000d_
-6. 940.000 - cashbon rokok (5 bks Lucky Stike 150 ribu (Pak Noge), 8 Bks Rocker (PakYanto) 1 Slop Classmild, 1 Slop Sampoerna)_x000d_
-7. 18.000 -  cashbon Weildin Point Coffe_x000d_
-8. 907.000 - (500.000 Bahan makanan dan perjalanan dinas ke tambua) dan (407.000) belanja tak bernota)_x000d_
-9. 480.000 - cashbon Bolang (1 Slop Brand Jati dan 1 Bks Surya Besar)_x000d_
-10. 300.000 - cashbon Lucky Stike (Andika)_x000d_
-11. 180.000 total belanja tak bernota (12 rb Air Mineral, 25 rb Baterai Alkaline, 28 rb Nescafe + Silver Queen, 24 rb Roti dan Air Mineral, 32 Kopi, 59 rb Snack dan Minuman, 100 ribu uang bungkus makanan untuk mekanik ke lokasi).</v>
+        <v xml:space="preserve">1. 300.000 - cashbon Lucky Stike (Andika)
+2. 180.000 total belanja tak bernota (12 rb Air Mineral, 25 rb Baterai Alkaline, 28 rb Nescafe + Silver Queen, 24 rb Roti dan Air Mineral, 32 Kopi, 59 rb Snack dan Minuman)
+3. 100 ribu uang bungkus makanan untuk mekanik ke lokasi.</v>
       </c>
     </row>
     <row r="16">
@@ -849,7 +832,7 @@
         <v>2026-05-17</v>
       </c>
       <c r="B16">
-        <v>1407500</v>
+        <v>1389500</v>
       </c>
       <c r="C16">
         <v>600000</v>
@@ -864,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>807500</v>
+        <v>789500</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -873,12 +856,12 @@
         <v/>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
+    <row r="17">
       <c r="A17" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="B17">
-        <v>1807500</v>
+        <v>1789500</v>
       </c>
       <c r="C17">
         <v>749200</v>
@@ -893,14 +876,13 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>713300</v>
+        <v>695300</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
-      <c r="I17" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 345.000 cashbon 1 Slop Sampoerna (Noge)_x000d_
-2. 300.000 uang makan pendamping pasien di puskesmas</v>
+      <c r="I17" t="str">
+        <v>1. 345.000 Cashbon 1 slop samporna (Noge)</v>
       </c>
     </row>
     <row r="18">
@@ -908,7 +890,7 @@
         <v>2026-05-19</v>
       </c>
       <c r="B18">
-        <v>6713300</v>
+        <v>6695300</v>
       </c>
       <c r="C18">
         <v>5050000</v>
@@ -923,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1663300</v>
+        <v>1645300</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -937,7 +919,7 @@
         <v>2026-05-20</v>
       </c>
       <c r="B19">
-        <v>2163300</v>
+        <v>2145300</v>
       </c>
       <c r="C19">
         <v>265000</v>
@@ -952,27 +934,27 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>94300</v>
+        <v>76300</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>1. Dana Pemeriksaan dan Perawatan Pasien an. Ahwal sebesar 504.000</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>1. 1.804.000 (504.000 biaya berobat Ahwal, 1.300.000 uang mobilisasi)</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v>2026-05-21</v>
       </c>
       <c r="B20">
-        <v>1081800</v>
+        <v>6076300</v>
       </c>
       <c r="C20">
-        <v>540000</v>
+        <v>4336000</v>
       </c>
       <c r="D20">
-        <v>175000</v>
+        <v>496000</v>
       </c>
       <c r="E20">
         <v>288000</v>
@@ -981,13 +963,15 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>78800</v>
+        <v>956300</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
-      <c r="I20" t="str">
-        <v>1. Casbon 5 Bungkus Classmild Isi 20 harga 175.000 (Wanto)</v>
+      <c r="I20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 175  Cashbon 5 Bks classmild isi 20 (Wanto)
+2. 288.000 transfer kembali ke rekening geost
+3. 321.000 Cashbon 1 slop classmild isi 20 (Wayan)</v>
       </c>
     </row>
   </sheetData>
